--- a/data/fmsForecastOutput/File1/RPT_RPT1665601280675FW_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT1665601280675FW_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1881,13 +1881,13 @@
         <v>506.7846169387016</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>539.8078041123414</v>
+        <v>539.8078041123413</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>566.7184588538407</v>
+        <v>566.7184588538406</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>593.9065092407632</v>
+        <v>593.9065092407631</v>
       </c>
       <c r="H8" s="148" t="n">
         <v>474.4341254786115</v>
@@ -1896,13 +1896,13 @@
         <v>503.3930187104816</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>537.3198278891163</v>
+        <v>537.3198278891161</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>565.2809616361691</v>
+        <v>565.280961636169</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>593.6532098588118</v>
+        <v>593.6532098588117</v>
       </c>
       <c r="M8" s="151" t="n">
         <v>52896349.07684423</v>
@@ -1914,7 +1914,7 @@
         <v>68512750.05748442</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>77801525.31451577</v>
+        <v>77801525.31451575</v>
       </c>
       <c r="Q8" s="153" t="n">
         <v>90267512.0945241</v>
@@ -1925,34 +1925,34 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>495.6274667399078</v>
+        <v>495.6274667399077</v>
       </c>
       <c r="U8" s="149" t="n">
         <v>524.6871670655826</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>558.8769233180093</v>
+        <v>558.8769233180092</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>586.7382173041783</v>
+        <v>586.7382173041781</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>614.8867061468775</v>
+        <v>614.8867061468774</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>491.9239842598317</v>
+        <v>491.9239842598316</v>
       </c>
       <c r="Z8" s="149" t="n">
         <v>521.7551062984435</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>556.7267942548425</v>
+        <v>556.7267942548424</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>585.4963480025333</v>
+        <v>585.4963480025331</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>614.6679547025863</v>
+        <v>614.6679547025861</v>
       </c>
       <c r="AD8" s="151" t="n">
         <v>52896349.07684423</v>
@@ -1964,7 +1964,7 @@
         <v>68512750.05748442</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>77801525.31451577</v>
+        <v>77801525.31451575</v>
       </c>
       <c r="AH8" s="153" t="n">
         <v>90267512.0945241</v>
@@ -2173,16 +2173,16 @@
         <v>587.0397240420771</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>615.8257354754819</v>
+        <v>615.8257354754818</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>652.559810932705</v>
+        <v>652.5598109327049</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>682.1607033597045</v>
+        <v>682.1607033597043</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>712.1218941358344</v>
+        <v>712.1218941358343</v>
       </c>
       <c r="H10" s="161" t="n">
         <v>581.7182480849186</v>
@@ -2194,10 +2194,10 @@
         <v>649.4265348373351</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>680.3079331278037</v>
+        <v>680.3079331278035</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>711.7025128655036</v>
+        <v>711.7025128655035</v>
       </c>
       <c r="M10" s="164" t="n">
         <v>79081771.07342969</v>
@@ -2220,34 +2220,34 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>605.3044909753359</v>
+        <v>605.3044909753357</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>635.0685387545975</v>
+        <v>635.0685387545974</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>672.9967167163874</v>
+        <v>672.9967167163873</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>703.5392261393408</v>
+        <v>703.5392261393406</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>734.4530021037724</v>
+        <v>734.4530021037723</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>600.5347822545243</v>
+        <v>600.5347822545242</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>631.2725970911366</v>
+        <v>631.2725970911365</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>670.1800935933502</v>
+        <v>670.1800935933501</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>701.8663116359357</v>
+        <v>701.8663116359354</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>734.0596552581666</v>
+        <v>734.0596552581665</v>
       </c>
       <c r="AD10" s="164" t="n">
         <v>79081771.07342969</v>
@@ -2333,7 +2333,7 @@
         <v>1390.253940210589</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>1207.006784360549</v>
+        <v>1207.006784360548</v>
       </c>
       <c r="I11" s="156" t="n">
         <v>1259.686928820142</v>
@@ -2371,7 +2371,7 @@
         <v>1476.343304116993</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1538.009421988317</v>
+        <v>1538.009421988318</v>
       </c>
       <c r="V11" s="156" t="n">
         <v>1610.040189979388</v>
@@ -2386,7 +2386,7 @@
         <v>1469.199197303926</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>1533.52954115518</v>
+        <v>1533.529541155181</v>
       </c>
       <c r="AA11" s="156" t="n">
         <v>1608.379044570821</v>
@@ -2461,40 +2461,40 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>623.5464283211918</v>
+        <v>623.5464283211917</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>654.0111407501352</v>
+        <v>654.011140750135</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>692.8347449273577</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>723.8398581678548</v>
+        <v>723.8398581678546</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>754.7825099294947</v>
+        <v>754.7825099294945</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>618.0593823539726</v>
+        <v>618.0593823539724</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>649.6781087871136</v>
+        <v>649.6781087871137</v>
       </c>
       <c r="J12" s="162" t="n">
         <v>689.6675854315775</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>721.9945810099119</v>
+        <v>721.9945810099117</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>754.3659529910042</v>
+        <v>754.365952991004</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>89206779.15589008</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>99862129.38298918</v>
+        <v>99862129.3829892</v>
       </c>
       <c r="O12" s="165" t="n">
         <v>112860117.7006035</v>
@@ -2517,34 +2517,34 @@
         <v>680.5931775077805</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>721.1693203275079</v>
+        <v>721.1693203275076</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>753.6214082301321</v>
+        <v>753.6214082301318</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>786.0160670297594</v>
+        <v>786.0160670297593</v>
       </c>
       <c r="Y12" s="161" t="n">
         <v>643.7339395416344</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>676.6299722545758</v>
+        <v>676.6299722545759</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>718.267648642198</v>
+        <v>718.2676486421979</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>751.9235017689936</v>
+        <v>751.9235017689932</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>785.6177422864325</v>
+        <v>785.6177422864324</v>
       </c>
       <c r="AD12" s="164" t="n">
         <v>89206779.15589008</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>99862129.38298918</v>
+        <v>99862129.3829892</v>
       </c>
       <c r="AF12" s="165" t="n">
         <v>112860117.7006035</v>
@@ -2603,46 +2603,46 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>6677.893717226249</v>
+        <v>6677.893717226247</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>6796.199828393556</v>
+        <v>6796.199828393555</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>7104.168020114192</v>
+        <v>7104.168020114189</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>7243.760854401225</v>
+        <v>7243.760854401223</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>7504.875527837427</v>
+        <v>7504.875527837425</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>6677.254077741672</v>
+        <v>6677.254077741668</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>6795.602709658777</v>
+        <v>6795.602709658774</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>7103.58883269225</v>
+        <v>7103.588832692248</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>7243.225595014702</v>
+        <v>7243.2255950147</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>7504.378226816273</v>
+        <v>7504.378226816271</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>62846962.67245874</v>
+        <v>62846962.67245871</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>71540911.47072144</v>
+        <v>71540911.47072141</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>83041387.84785938</v>
+        <v>83041387.84785935</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>95317771.45889692</v>
+        <v>95317771.45889689</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>112357039.2962067</v>
@@ -2653,46 +2653,46 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>4080.111470312187</v>
+        <v>4080.111470312186</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>4152.395058764124</v>
+        <v>4152.395058764122</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>4340.559861131266</v>
+        <v>4340.559861131265</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>4425.849377326875</v>
+        <v>4425.849377326874</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>4585.387252481377</v>
+        <v>4585.387252481375</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>4079.827928150463</v>
+        <v>4079.827928150462</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>4152.130365960325</v>
+        <v>4152.130365960324</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>4340.303117426539</v>
+        <v>4340.303117426537</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>4425.612106653087</v>
+        <v>4425.612106653086</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>4585.166808516748</v>
+        <v>4585.166808516746</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>62846962.67245874</v>
+        <v>62846962.67245871</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>71540911.47072144</v>
+        <v>71540911.47072141</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>83041387.84785938</v>
+        <v>83041387.84785935</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>95317771.45889692</v>
+        <v>95317771.45889689</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>112357039.2962067</v>
@@ -2746,31 +2746,31 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>997.2387216279361</v>
+        <v>997.2387216279357</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>1050.145387191725</v>
+        <v>1050.145387191724</v>
       </c>
       <c r="E14" s="168" t="n">
         <v>1122.096443479686</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>1176.749953779059</v>
+        <v>1176.749953779058</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>1235.525193640785</v>
+        <v>1235.525193640784</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>988.9946533044891</v>
+        <v>988.9946533044887</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>1043.627899833212</v>
+        <v>1043.627899833211</v>
       </c>
       <c r="J14" s="168" t="n">
         <v>1117.302893604357</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>1173.951959467464</v>
+        <v>1173.951959467463</v>
       </c>
       <c r="L14" s="169" t="n">
         <v>1234.886032679779</v>
@@ -2779,7 +2779,7 @@
         <v>152053741.8283488</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>171403040.8537107</v>
+        <v>171403040.8537106</v>
       </c>
       <c r="O14" s="171" t="n">
         <v>195901505.5484629</v>
@@ -2788,7 +2788,7 @@
         <v>222907303.1726156</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>259720046.8546799</v>
+        <v>259720046.8546798</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>994.4046031963546</v>
+        <v>994.4046031963544</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>1045.415172627006</v>
+        <v>1045.415172627005</v>
       </c>
       <c r="V14" s="168" t="n">
         <v>1115.43754974965</v>
@@ -2811,10 +2811,10 @@
         <v>1225.185914635225</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>987.4811516234029</v>
+        <v>987.4811516234026</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>1039.956979815639</v>
+        <v>1039.956979815638</v>
       </c>
       <c r="AA14" s="168" t="n">
         <v>1111.429516224945</v>
@@ -2823,13 +2823,13 @@
         <v>1165.699340627499</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>1224.629967252641</v>
+        <v>1224.62996725264</v>
       </c>
       <c r="AD14" s="170" t="n">
         <v>152053741.8283488</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>171403040.8537107</v>
+        <v>171403040.8537106</v>
       </c>
       <c r="AF14" s="171" t="n">
         <v>195901505.5484629</v>
@@ -2838,7 +2838,7 @@
         <v>222907303.1726156</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>259720046.8546799</v>
+        <v>259720046.8546798</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>110496.2019156367</v>
       </c>
       <c r="D19" s="75" t="n">
-        <v>118678.4478102867</v>
+        <v>118678.4478102868</v>
       </c>
       <c r="E19" s="75" t="n">
         <v>126920.636447905</v>
@@ -3188,7 +3188,7 @@
         <v>119478.0409678406</v>
       </c>
       <c r="O19" s="75" t="n">
-        <v>127508.3227928507</v>
+        <v>127508.3227928508</v>
       </c>
       <c r="P19" s="75" t="n">
         <v>137633.3727732919</v>
@@ -3241,7 +3241,7 @@
         <v>123063.5039744874</v>
       </c>
       <c r="AG19" s="75" t="n">
-        <v>132881.316134493</v>
+        <v>132881.3161344931</v>
       </c>
       <c r="AH19" s="76" t="n">
         <v>146855.7314626903</v>
@@ -3295,7 +3295,7 @@
         <v>25005.54406696305</v>
       </c>
       <c r="E20" s="80" t="n">
-        <v>26179.22989067978</v>
+        <v>26179.22989067979</v>
       </c>
       <c r="F20" s="80" t="n">
         <v>28134.28005717414</v>
@@ -3448,7 +3448,7 @@
         <v>153838.5244094676</v>
       </c>
       <c r="P21" s="86" t="n">
-        <v>165869.0475564155</v>
+        <v>165869.0475564156</v>
       </c>
       <c r="Q21" s="87" t="n">
         <v>183064.5489001492</v>
@@ -3468,7 +3468,7 @@
         <v>148450.6794018013</v>
       </c>
       <c r="W21" s="86" t="n">
-        <v>160391.950754759</v>
+        <v>160391.9507547591</v>
       </c>
       <c r="X21" s="87" t="n">
         <v>177393.9232267138</v>
@@ -3492,7 +3492,7 @@
         <v>131685.5799368379</v>
       </c>
       <c r="AE21" s="86" t="n">
-        <v>140168.1308227071</v>
+        <v>140168.1308227072</v>
       </c>
       <c r="AF21" s="86" t="n">
         <v>149074.5857520956</v>
@@ -3569,10 +3569,10 @@
         <v>8350.761245883758</v>
       </c>
       <c r="D22" s="80" t="n">
-        <v>9007.794486587551</v>
+        <v>9007.794486587552</v>
       </c>
       <c r="E22" s="80" t="n">
-        <v>9796.291117312727</v>
+        <v>9796.291117312729</v>
       </c>
       <c r="F22" s="80" t="n">
         <v>10849.08173376411</v>
@@ -3599,10 +3599,10 @@
         <v>8388.526239994959</v>
       </c>
       <c r="N22" s="80" t="n">
-        <v>9032.267580791255</v>
+        <v>9032.267580791256</v>
       </c>
       <c r="O22" s="80" t="n">
-        <v>9805.700844323821</v>
+        <v>9805.700844323823</v>
       </c>
       <c r="P22" s="80" t="n">
         <v>10849.08173376411</v>
@@ -3619,13 +3619,13 @@
         <v>6858.166426619998</v>
       </c>
       <c r="U22" s="80" t="n">
-        <v>7397.763138810662</v>
+        <v>7397.763138810664</v>
       </c>
       <c r="V22" s="80" t="n">
-        <v>8045.325793413907</v>
+        <v>8045.325793413908</v>
       </c>
       <c r="W22" s="80" t="n">
-        <v>8909.943167496587</v>
+        <v>8909.943167496589</v>
       </c>
       <c r="X22" s="81" t="n">
         <v>10086.98682050258</v>
@@ -3649,13 +3649,13 @@
         <v>6891.514847707808</v>
       </c>
       <c r="AE22" s="80" t="n">
-        <v>7419.374132537382</v>
+        <v>7419.374132537384</v>
       </c>
       <c r="AF22" s="80" t="n">
-        <v>8053.63506357461</v>
+        <v>8053.635063574611</v>
       </c>
       <c r="AG22" s="80" t="n">
-        <v>8909.943167496587</v>
+        <v>8909.943167496589</v>
       </c>
       <c r="AH22" s="81" t="n">
         <v>10086.98682050258</v>
@@ -3706,16 +3706,16 @@
         <v>143063.5716991698</v>
       </c>
       <c r="D23" s="86" t="n">
-        <v>152691.7863638373</v>
+        <v>152691.7863638374</v>
       </c>
       <c r="E23" s="86" t="n">
         <v>162896.1574558975</v>
       </c>
       <c r="F23" s="86" t="n">
-        <v>176267.6236656359</v>
+        <v>176267.623665636</v>
       </c>
       <c r="G23" s="87" t="n">
-        <v>195239.0332577241</v>
+        <v>195239.0332577242</v>
       </c>
       <c r="H23" s="85" t="n">
         <v>1270.098661326248</v>
@@ -3759,10 +3759,10 @@
         <v>146728.0788042392</v>
       </c>
       <c r="V23" s="86" t="n">
-        <v>156496.0051952152</v>
+        <v>156496.0051952153</v>
       </c>
       <c r="W23" s="86" t="n">
-        <v>169301.8939222556</v>
+        <v>169301.8939222557</v>
       </c>
       <c r="X23" s="87" t="n">
         <v>187480.9100472164</v>
@@ -3771,7 +3771,7 @@
         <v>1071.011065912703</v>
       </c>
       <c r="Z23" s="86" t="n">
-        <v>859.4261510053072</v>
+        <v>859.4261510053074</v>
       </c>
       <c r="AA23" s="86" t="n">
         <v>632.2156204549408</v>
@@ -3945,7 +3945,7 @@
         <v>152474.7671050415</v>
       </c>
       <c r="D25" s="92" t="n">
-        <v>163218.3914191851</v>
+        <v>163218.3914191852</v>
       </c>
       <c r="E25" s="92" t="n">
         <v>174585.2655418469</v>
@@ -3984,7 +3984,7 @@
         <v>189877.7044281543</v>
       </c>
       <c r="Q25" s="93" t="n">
-        <v>210319.0415807613</v>
+        <v>210319.0415807614</v>
       </c>
       <c r="S25" s="51" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>163956.9095051442</v>
       </c>
       <c r="V25" s="92" t="n">
-        <v>175627.4975613213</v>
+        <v>175627.4975613214</v>
       </c>
       <c r="W25" s="92" t="n">
         <v>190838.4992905267</v>
@@ -4010,7 +4010,7 @@
         <v>1072.081569346541</v>
       </c>
       <c r="Z25" s="92" t="n">
-        <v>860.5244661116376</v>
+        <v>860.5244661116377</v>
       </c>
       <c r="AA25" s="92" t="n">
         <v>633.3473133561454</v>
@@ -4034,7 +4034,7 @@
         <v>191221.9518393345</v>
       </c>
       <c r="AH25" s="93" t="n">
-        <v>212080.4273941956</v>
+        <v>212080.4273941957</v>
       </c>
     </row>
     <row r="28" ht="1.95" customHeight="1">
@@ -4414,13 +4414,13 @@
         <v>533.3291411990961</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>571.7068408263463</v>
+        <v>571.7068408263461</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>607.8228420888065</v>
+        <v>607.8228420888063</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>638.5852069001241</v>
+        <v>638.585206900124</v>
       </c>
       <c r="H35" s="148" t="n">
         <v>487.8118631917249</v>
@@ -4429,25 +4429,25 @@
         <v>529.7598967708111</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>569.0718418215241</v>
+        <v>569.071841821524</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>606.2810824536837</v>
+        <v>606.2810824536834</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>638.3128521848377</v>
+        <v>638.3128521848375</v>
       </c>
       <c r="M35" s="151" t="n">
         <v>54387880.6634843</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>63294674.64950197</v>
+        <v>63294674.64950198</v>
       </c>
       <c r="O35" s="152" t="n">
         <v>72561396.099301</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>83444510.22674274</v>
+        <v>83444510.22674273</v>
       </c>
       <c r="Q35" s="153" t="n">
         <v>97058201.90610689</v>
@@ -4458,46 +4458,46 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>509.6027983979595</v>
+        <v>509.6027983979594</v>
       </c>
       <c r="U35" s="149" t="n">
         <v>552.169396734315</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>591.9028176450594</v>
+        <v>591.9028176450593</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>629.294643984629</v>
+        <v>629.2946439846288</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>661.1437126137988</v>
+        <v>661.1437126137987</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>505.7948878959876</v>
+        <v>505.7948878959875</v>
       </c>
       <c r="Z35" s="149" t="n">
         <v>549.0837595649631</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>589.6256303115171</v>
+        <v>589.6256303115169</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>627.9627012595671</v>
+        <v>627.9627012595669</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>660.9085048258072</v>
+        <v>660.9085048258071</v>
       </c>
       <c r="AD35" s="151" t="n">
         <v>54387880.6634843</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>63294674.64950197</v>
+        <v>63294674.64950198</v>
       </c>
       <c r="AF35" s="152" t="n">
         <v>72561396.099301</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>83444510.22674274</v>
+        <v>83444510.22674273</v>
       </c>
       <c r="AH35" s="153" t="n">
         <v>97058201.90610689</v>
@@ -4563,7 +4563,7 @@
         <v>1125.868532097438</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1207.818301388124</v>
+        <v>1207.818301388123</v>
       </c>
       <c r="V36" s="156" t="n">
         <v>1286.170841097506</v>
@@ -4572,7 +4572,7 @@
         <v>1352.752784845934</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1407.193250530019</v>
+        <v>1407.193250530018</v>
       </c>
       <c r="Y36" s="155" t="n">
         <v>1114.954371831499</v>
@@ -4581,7 +4581,7 @@
         <v>1198.423310693407</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>1278.731409939025</v>
+        <v>1278.731409939024</v>
       </c>
       <c r="AB36" s="156" t="n">
         <v>1347.852249899613</v>
@@ -4615,16 +4615,16 @@
         <v>603.6603861006104</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>648.1534070748185</v>
+        <v>648.1534070748183</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>691.1997110486791</v>
+        <v>691.199711048679</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>731.7200398084702</v>
+        <v>731.7200398084701</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>765.7813492471375</v>
+        <v>765.7813492471374</v>
       </c>
       <c r="H37" s="161" t="n">
         <v>598.1882449500856</v>
@@ -4636,10 +4636,10 @@
         <v>687.8809048711122</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>729.7326648377847</v>
+        <v>729.7326648377845</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>765.3303669677167</v>
+        <v>765.3303669677166</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>81320787.17092901</v>
@@ -4651,7 +4651,7 @@
         <v>105822583.3748212</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>121040062.0874484</v>
+        <v>121040062.0874483</v>
       </c>
       <c r="Q37" s="166" t="n">
         <v>140104858.3885307</v>
@@ -4662,34 +4662,34 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>622.4422773550059</v>
+        <v>622.4422773550058</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>668.4063581753426</v>
+        <v>668.4063581753425</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>712.8467434520691</v>
+        <v>712.8467434520689</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>754.6517235925378</v>
+        <v>754.6517235925376</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>789.7951397662774</v>
+        <v>789.7951397662773</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>617.5375254445779</v>
+        <v>617.5375254445778</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>664.4111491730266</v>
+        <v>664.4111491730265</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>709.8633401591301</v>
+        <v>709.86334015913</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>752.857270964295</v>
+        <v>752.8572709642947</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>789.3721536446168</v>
+        <v>789.3721536446167</v>
       </c>
       <c r="AD37" s="164" t="n">
         <v>81320787.17092901</v>
@@ -4701,7 +4701,7 @@
         <v>105822583.3748212</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>121040062.0874484</v>
+        <v>121040062.0874483</v>
       </c>
       <c r="AH37" s="166" t="n">
         <v>140104858.3885307</v>
@@ -4744,16 +4744,16 @@
         <v>1495.242582777069</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>10412897.97111799</v>
+        <v>10412897.97111798</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>11976639.76851665</v>
+        <v>11976639.76851666</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>13722222.93853281</v>
+        <v>13722222.93853282</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>15821187.05678568</v>
+        <v>15821187.05678569</v>
       </c>
       <c r="Q38" s="160" t="n">
         <v>18365009.49914744</v>
@@ -4764,10 +4764,10 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1518.32098018215</v>
+        <v>1518.320980182149</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>1618.954208696405</v>
+        <v>1618.954208696406</v>
       </c>
       <c r="V38" s="156" t="n">
         <v>1705.614326987994</v>
@@ -4779,10 +4779,10 @@
         <v>1820.663576343646</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>1510.973741075437</v>
+        <v>1510.973741075436</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>1614.238553625912</v>
+        <v>1614.238553625913</v>
       </c>
       <c r="AA38" s="156" t="n">
         <v>1703.854573768357</v>
@@ -4794,16 +4794,16 @@
         <v>1820.663576343646</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>10412897.97111799</v>
+        <v>10412897.97111798</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>11976639.76851665</v>
+        <v>11976639.76851666</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>13722222.93853281</v>
+        <v>13722222.93853282</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>15821187.05678568</v>
+        <v>15821187.05678569</v>
       </c>
       <c r="AH38" s="160" t="n">
         <v>18365009.49914744</v>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>641.2092474172397</v>
+        <v>641.2092474172396</v>
       </c>
       <c r="D39" s="162" t="n">
         <v>688.353389195526</v>
@@ -4825,13 +4825,13 @@
         <v>733.8712476733501</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>776.4400875106124</v>
+        <v>776.4400875106121</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>811.6710334172313</v>
+        <v>811.6710334172311</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>635.566773247903</v>
+        <v>635.5667732479029</v>
       </c>
       <c r="I39" s="162" t="n">
         <v>683.7928289062665</v>
@@ -4840,10 +4840,10 @@
         <v>730.5164977740903</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>774.4607171542729</v>
+        <v>774.4607171542726</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>811.2230802700748</v>
+        <v>811.2230802700744</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>91733685.14204699</v>
@@ -4855,7 +4855,7 @@
         <v>119544806.313354</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>136861249.1442341</v>
+        <v>136861249.144234</v>
       </c>
       <c r="Q39" s="166" t="n">
         <v>158469867.8876781</v>
@@ -4869,31 +4869,31 @@
         <v>667.1245566832798</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>716.3312537206747</v>
+        <v>716.3312537206748</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>763.884075917671</v>
+        <v>763.8840759176708</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>808.3858129022556</v>
+        <v>808.3858129022552</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>845.2586871258951</v>
+        <v>845.258687125895</v>
       </c>
       <c r="Y39" s="161" t="n">
         <v>661.9685979466591</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>712.1599398115693</v>
+        <v>712.1599398115694</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>760.8105386338848</v>
+        <v>760.8105386338847</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>806.5645224242649</v>
+        <v>806.5645224242645</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>844.8303403481167</v>
+        <v>844.8303403481166</v>
       </c>
       <c r="AD39" s="164" t="n">
         <v>91733685.14204699</v>
@@ -4905,7 +4905,7 @@
         <v>119544806.313354</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>136861249.1442341</v>
+        <v>136861249.144234</v>
       </c>
       <c r="AH39" s="166" t="n">
         <v>158469867.8876781</v>
@@ -4918,46 +4918,46 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>6868.847682808321</v>
+        <v>6868.847682808318</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>7154.647677011851</v>
+        <v>7154.647677011848</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>7527.196461235634</v>
+        <v>7527.196461235631</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>7772.2755948511</v>
+        <v>7772.275594851098</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>8072.362620025199</v>
+        <v>8072.362620025197</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>6868.1897528715</v>
+        <v>6868.189752871496</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>7154.019064805534</v>
+        <v>7154.019064805531</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>7526.582785221711</v>
+        <v>7526.582785221708</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>7771.701282204616</v>
+        <v>7771.701282204614</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>8071.827715194443</v>
+        <v>8071.82771519444</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>64644067.7560777</v>
+        <v>64644067.75607767</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>75314150.40606532</v>
+        <v>75314150.40606529</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>87986213.01955858</v>
+        <v>87986213.01955855</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>102272286.9730654</v>
+        <v>102272286.9730653</v>
       </c>
       <c r="Q40" s="160" t="n">
         <v>120853005.589122</v>
@@ -4968,46 +4968,46 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>4196.782010195626</v>
+        <v>4196.782010195624</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>4371.402314732208</v>
+        <v>4371.402314732206</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>4599.025070069153</v>
+        <v>4599.025070069151</v>
       </c>
       <c r="W40" s="156" t="n">
         <v>4748.765426316389</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>4932.114932216174</v>
+        <v>4932.114932216172</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>4196.490360162995</v>
+        <v>4196.490360162993</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>4371.123661396279</v>
+        <v>4371.123661396277</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>4598.753038171793</v>
+        <v>4598.753038171792</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>4748.510844048376</v>
+        <v>4748.510844048375</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>4931.877819206999</v>
+        <v>4931.877819206998</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>64644067.7560777</v>
+        <v>64644067.75607767</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>75314150.40606532</v>
+        <v>75314150.40606529</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>87986213.01955858</v>
+        <v>87986213.01955855</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>102272286.9730654</v>
+        <v>102272286.9730653</v>
       </c>
       <c r="AH40" s="160" t="n">
         <v>120853005.589122</v>
@@ -5023,16 +5023,16 @@
         <v>1025.597584880352</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>1105.390498479848</v>
+        <v>1105.390498479847</v>
       </c>
       <c r="E41" s="180" t="n">
         <v>1188.708673030422</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>1262.409860816195</v>
+        <v>1262.409860816194</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>1328.778627295653</v>
+        <v>1328.778627295652</v>
       </c>
       <c r="H41" s="179" t="n">
         <v>1017.119076797239</v>
@@ -5041,13 +5041,13 @@
         <v>1098.530144963152</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>1183.63055844899</v>
+        <v>1183.630558448989</v>
       </c>
       <c r="K41" s="180" t="n">
         <v>1259.408190326961</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>1328.091224538706</v>
+        <v>1328.091224538705</v>
       </c>
       <c r="M41" s="182" t="n">
         <v>156377752.8981247</v>
@@ -5062,7 +5062,7 @@
         <v>239133536.1172994</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>279322873.4768002</v>
+        <v>279322873.4768001</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5076,10 +5076,10 @@
         <v>1100.411441008963</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>1181.654480161639</v>
+        <v>1181.654480161638</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>1253.067578116143</v>
+        <v>1253.067578116142</v>
       </c>
       <c r="X41" s="187" t="n">
         <v>1317.658973050683</v>
@@ -5094,7 +5094,7 @@
         <v>1177.408513390869</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>1250.554833360453</v>
+        <v>1250.554833360452</v>
       </c>
       <c r="AC41" s="187" t="n">
         <v>1317.061064563117</v>
@@ -5112,7 +5112,7 @@
         <v>239133536.1172994</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>279322873.4768002</v>
+        <v>279322873.4768001</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5377,25 +5377,25 @@
         <v>0.1820885246526054</v>
       </c>
       <c r="E46" s="149" t="n">
-        <v>0.2018103886359686</v>
+        <v>0.2018103886359685</v>
       </c>
       <c r="F46" s="149" t="n">
         <v>0.2216682562048453</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.2388240245289702</v>
+        <v>0.2388240245289701</v>
       </c>
       <c r="H46" s="148" t="n">
-        <v>0.1641628339753153</v>
+        <v>0.1641628339753152</v>
       </c>
       <c r="I46" s="149" t="n">
         <v>0.1808699179764172</v>
       </c>
       <c r="J46" s="149" t="n">
-        <v>0.2008802437868184</v>
+        <v>0.2008802437868183</v>
       </c>
       <c r="K46" s="149" t="n">
-        <v>0.2211059884746129</v>
+        <v>0.2211059884746128</v>
       </c>
       <c r="L46" s="150" t="n">
         <v>0.2387221667839091</v>
@@ -5427,25 +5427,25 @@
         <v>0.1885209395901673</v>
       </c>
       <c r="V46" s="149" t="n">
-        <v>0.2089394933442075</v>
+        <v>0.2089394933442074</v>
       </c>
       <c r="W46" s="149" t="n">
-        <v>0.2294988551133468</v>
+        <v>0.2294988551133467</v>
       </c>
       <c r="X46" s="150" t="n">
-        <v>0.2472606639369704</v>
+        <v>0.2472606639369703</v>
       </c>
       <c r="Y46" s="148" t="n">
-        <v>0.1702146431289184</v>
+        <v>0.1702146431289183</v>
       </c>
       <c r="Z46" s="149" t="n">
         <v>0.1874674454598498</v>
       </c>
       <c r="AA46" s="149" t="n">
-        <v>0.2081356546843188</v>
+        <v>0.2081356546843187</v>
       </c>
       <c r="AB46" s="149" t="n">
-        <v>0.229013105975959</v>
+        <v>0.2290131059759589</v>
       </c>
       <c r="AC46" s="150" t="n">
         <v>0.2471726987446644</v>
@@ -5494,7 +5494,7 @@
         <v>0.027796429498319</v>
       </c>
       <c r="J47" s="156" t="n">
-        <v>0.02762792131526165</v>
+        <v>0.02762792131526164</v>
       </c>
       <c r="K47" s="156" t="n">
         <v>0.02679912271076802</v>
@@ -5526,7 +5526,7 @@
         <v>0.02827175368349494</v>
       </c>
       <c r="U47" s="156" t="n">
-        <v>0.0283575399860892</v>
+        <v>0.02835753998608919</v>
       </c>
       <c r="V47" s="156" t="n">
         <v>0.02812958383218289</v>
@@ -5535,13 +5535,13 @@
         <v>0.02722705827471923</v>
       </c>
       <c r="X47" s="157" t="n">
-        <v>0.02573047774275254</v>
+        <v>0.02573047774275253</v>
       </c>
       <c r="Y47" s="155" t="n">
         <v>0.02799768753642361</v>
       </c>
       <c r="Z47" s="156" t="n">
-        <v>0.02813696142390963</v>
+        <v>0.02813696142390962</v>
       </c>
       <c r="AA47" s="156" t="n">
         <v>0.02796687752929571</v>
@@ -5550,7 +5550,7 @@
         <v>0.02712842447255265</v>
       </c>
       <c r="AC47" s="157" t="n">
-        <v>0.02569451808483585</v>
+        <v>0.02569451808483584</v>
       </c>
       <c r="AD47" s="158" t="n">
         <v>676.3138652969975</v>
@@ -5578,7 +5578,7 @@
         <v>0.1408879555542316</v>
       </c>
       <c r="D48" s="162" t="n">
-        <v>0.1552744269920273</v>
+        <v>0.1552744269920272</v>
       </c>
       <c r="E48" s="162" t="n">
         <v>0.1720533945320395</v>
@@ -5599,10 +5599,10 @@
         <v>0.171227277478579</v>
       </c>
       <c r="K48" s="162" t="n">
-        <v>0.1880293804476092</v>
+        <v>0.1880293804476091</v>
       </c>
       <c r="L48" s="163" t="n">
-        <v>0.2025833742962913</v>
+        <v>0.2025833742962912</v>
       </c>
       <c r="M48" s="164" t="n">
         <v>18979.4124517282</v>
@@ -5631,13 +5631,13 @@
         <v>0.1601263113495038</v>
       </c>
       <c r="V48" s="162" t="n">
-        <v>0.1774417726621427</v>
+        <v>0.1774417726621426</v>
       </c>
       <c r="W48" s="162" t="n">
         <v>0.1944502457929139</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.2090592132788226</v>
+        <v>0.2090592132788225</v>
       </c>
       <c r="Y48" s="161" t="n">
         <v>0.1441267332446844</v>
@@ -5646,13 +5646,13 @@
         <v>0.1591692018415129</v>
       </c>
       <c r="AA48" s="162" t="n">
-        <v>0.1766991440765065</v>
+        <v>0.1766991440765064</v>
       </c>
       <c r="AB48" s="162" t="n">
-        <v>0.1939878712382459</v>
+        <v>0.1939878712382458</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.2089472486168871</v>
+        <v>0.208947248616887</v>
       </c>
       <c r="AD48" s="164" t="n">
         <v>18979.4124517282</v>
@@ -5719,7 +5719,7 @@
         <v>1751.512339086387</v>
       </c>
       <c r="Q49" s="160" t="n">
-        <v>1944.399517948366</v>
+        <v>1944.399517948365</v>
       </c>
       <c r="S49" s="32" t="inlineStr">
         <is>
@@ -5733,28 +5733,28 @@
         <v>0.1952985192193826</v>
       </c>
       <c r="V49" s="156" t="n">
-        <v>0.1971838862399236</v>
+        <v>0.1971838862399235</v>
       </c>
       <c r="W49" s="156" t="n">
-        <v>0.1965795186523627</v>
+        <v>0.1965795186523626</v>
       </c>
       <c r="X49" s="157" t="n">
-        <v>0.1927631663001903</v>
+        <v>0.1927631663001902</v>
       </c>
       <c r="Y49" s="155" t="n">
         <v>0.192339009780085</v>
       </c>
       <c r="Z49" s="156" t="n">
-        <v>0.1947296578844112</v>
+        <v>0.1947296578844111</v>
       </c>
       <c r="AA49" s="156" t="n">
         <v>0.1969804434256948</v>
       </c>
       <c r="AB49" s="156" t="n">
-        <v>0.1965795186523627</v>
+        <v>0.1965795186523626</v>
       </c>
       <c r="AC49" s="157" t="n">
-        <v>0.1927631663001903</v>
+        <v>0.1927631663001902</v>
       </c>
       <c r="AD49" s="158" t="n">
         <v>1325.507141692873</v>
@@ -5769,7 +5769,7 @@
         <v>1751.512339086387</v>
       </c>
       <c r="AH49" s="160" t="n">
-        <v>1944.399517948366</v>
+        <v>1944.399517948365</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickTop="1">
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="C50" s="161" t="n">
-        <v>0.1419293489758365</v>
+        <v>0.1419293489758364</v>
       </c>
       <c r="D50" s="162" t="n">
         <v>0.1555762903749652</v>
@@ -5788,13 +5788,13 @@
         <v>0.1714451755531917</v>
       </c>
       <c r="F50" s="162" t="n">
-        <v>0.1868736067437889</v>
+        <v>0.1868736067437888</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.1999099918541769</v>
+        <v>0.1999099918541768</v>
       </c>
       <c r="H50" s="161" t="n">
-        <v>0.1406804077157211</v>
+        <v>0.140680407715721</v>
       </c>
       <c r="I50" s="162" t="n">
         <v>0.1545455479351502</v>
@@ -5806,7 +5806,7 @@
         <v>0.1863972118699012</v>
       </c>
       <c r="L50" s="163" t="n">
-        <v>0.1997996635237176</v>
+        <v>0.1997996635237174</v>
       </c>
       <c r="M50" s="164" t="n">
         <v>20304.91959342107</v>
@@ -5841,7 +5841,7 @@
         <v>0.194562304197733</v>
       </c>
       <c r="X50" s="163" t="n">
-        <v>0.2081824412860989</v>
+        <v>0.2081824412860988</v>
       </c>
       <c r="Y50" s="161" t="n">
         <v>0.1465243561714898</v>
@@ -5856,7 +5856,7 @@
         <v>0.194123955990286</v>
       </c>
       <c r="AC50" s="163" t="n">
-        <v>0.2080769418936961</v>
+        <v>0.208076941893696</v>
       </c>
       <c r="AD50" s="164" t="n">
         <v>20304.91959342107</v>
@@ -6010,7 +6010,7 @@
         <v>0.1734788541169557</v>
       </c>
       <c r="L52" s="181" t="n">
-        <v>0.1855763189809973</v>
+        <v>0.1855763189809972</v>
       </c>
       <c r="M52" s="182" t="n">
         <v>20304.91959342107</v>
@@ -6045,7 +6045,7 @@
         <v>0.1726054580653966</v>
       </c>
       <c r="X52" s="187" t="n">
-        <v>0.1841186037321795</v>
+        <v>0.1841186037321794</v>
       </c>
       <c r="Y52" s="185" t="n">
         <v>0.1318660438252615</v>
@@ -6060,7 +6060,7 @@
         <v>0.1722593367012087</v>
       </c>
       <c r="AC52" s="187" t="n">
-        <v>0.1840350570193033</v>
+        <v>0.1840350570193032</v>
       </c>
       <c r="AD52" s="188" t="n">
         <v>20304.91959342107</v>
@@ -6334,13 +6334,13 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.00941735619438662</v>
+        <v>0.009417356194386618</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.008600077056639933</v>
+        <v>0.008600077056639932</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007897561678242914</v>
+        <v>0.007897561678242912</v>
       </c>
       <c r="F57" s="149" t="n">
         <v>0.0002850966978455696</v>
@@ -6349,13 +6349,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.009333113971321933</v>
+        <v>0.009333113971321931</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.008542522022148063</v>
+        <v>0.008542522022148061</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.007861161786416165</v>
+        <v>0.007861161786416163</v>
       </c>
       <c r="K57" s="149" t="n">
         <v>0.0002843735420995062</v>
@@ -6370,10 +6370,10 @@
         <v>1020.643796130887</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>39.13928972664274</v>
+        <v>39.13928972664275</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6384,13 +6384,13 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.009750031428988486</v>
+        <v>0.009750031428988485</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.008903881287185783</v>
+        <v>0.008903881287185781</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.008176549021384743</v>
+        <v>0.008176549021384741</v>
       </c>
       <c r="W57" s="149" t="n">
         <v>0.0002951679544575395</v>
@@ -6402,10 +6402,10 @@
         <v>0.009677176163692224</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.008854124550912952</v>
+        <v>0.00885412455091295</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.008145091942099896</v>
+        <v>0.008145091942099895</v>
       </c>
       <c r="AB57" s="149" t="n">
         <v>0.0002945432124334826</v>
@@ -6420,10 +6420,10 @@
         <v>1020.643796130887</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>39.13928972664274</v>
+        <v>39.13928972664275</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6541,10 +6541,10 @@
         <v>0.007724447942738562</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.007103392540783734</v>
+        <v>0.007103392540783732</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006547122336295313</v>
+        <v>0.006547122336295312</v>
       </c>
       <c r="F59" s="162" t="n">
         <v>0.0002366076333979681</v>
@@ -6556,7 +6556,7 @@
         <v>0.007654426337170592</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.007054593779841191</v>
+        <v>0.00705459377984119</v>
       </c>
       <c r="J59" s="162" t="n">
         <v>0.006515686226430601</v>
@@ -6574,10 +6574,10 @@
         <v>1020.643796130887</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>39.13928972664274</v>
+        <v>39.13928972664275</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.00796478132323071</v>
+        <v>0.007964781323230708</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.007325353360870443</v>
+        <v>0.007325353360870441</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.006752165491113359</v>
+        <v>0.006752165491113357</v>
       </c>
       <c r="W59" s="162" t="n">
         <v>0.0002440227800863095</v>
@@ -6603,13 +6603,13 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.007902020039441859</v>
+        <v>0.007902020039441857</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.007281568143488029</v>
+        <v>0.007281568143488027</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.006723906355547832</v>
+        <v>0.00672390635554783</v>
       </c>
       <c r="AB59" s="162" t="n">
         <v>0.0002434425292164215</v>
@@ -6624,10 +6624,10 @@
         <v>1020.643796130887</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>39.13928972664274</v>
+        <v>39.13928972664275</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.007273564326735273</v>
+        <v>0.007273564326735271</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006684339874699444</v>
+        <v>0.006684339874699442</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.00615338980516195</v>
+        <v>0.006153389805161949</v>
       </c>
       <c r="F61" s="162" t="n">
         <v>0.0002220446892781995</v>
@@ -6757,10 +6757,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.007209558857385099</v>
+        <v>0.007209558857385097</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.006640053995569693</v>
+        <v>0.006640053995569692</v>
       </c>
       <c r="J61" s="162" t="n">
         <v>0.006125260778586212</v>
@@ -6778,10 +6778,10 @@
         <v>1020.643796130887</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>39.13928972664274</v>
+        <v>39.13928972664275</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6795,10 +6795,10 @@
         <v>0.007567534929550247</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.006956022354062191</v>
+        <v>0.00695602235406219</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.006405042437593303</v>
+        <v>0.006405042437593302</v>
       </c>
       <c r="W61" s="162" t="n">
         <v>0.000231180460063936</v>
@@ -6810,10 +6810,10 @@
         <v>0.007509048253495806</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.00691551629957017</v>
+        <v>0.006915516299570169</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006379271332582996</v>
+        <v>0.006379271332582994</v>
       </c>
       <c r="AB61" s="162" t="n">
         <v>0.0002306596112762756</v>
@@ -6828,10 +6828,10 @@
         <v>1020.643796130887</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>39.13928972664274</v>
+        <v>39.13928972664275</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6946,13 +6946,13 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.006824618337338058</v>
+        <v>0.006824618337338056</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006253240135847324</v>
+        <v>0.006253240135847321</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.005741398344689725</v>
+        <v>0.005741398344689724</v>
       </c>
       <c r="F63" s="180" t="n">
         <v>0.0002066202260816289</v>
@@ -6961,13 +6961,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.006768199930557163</v>
+        <v>0.006768199930557162</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.006214430829981477</v>
+        <v>0.006214430829981476</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.005716871326999468</v>
+        <v>0.005716871326999467</v>
       </c>
       <c r="K63" s="180" t="n">
         <v>0.0002061289388583915</v>
@@ -6982,10 +6982,10 @@
         <v>1020.643796130887</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>39.13928972664274</v>
+        <v>39.13928972664275</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -6999,10 +6999,10 @@
         <v>0.006805223004807463</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006225073400147639</v>
+        <v>0.006225073400147638</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.005707326976171227</v>
+        <v>0.005707326976171225</v>
       </c>
       <c r="W63" s="186" t="n">
         <v>0.0002050911628007423</v>
@@ -7014,10 +7014,10 @@
         <v>0.006757842258815866</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.006192571814392445</v>
+        <v>0.006192571814392444</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.005686819187221428</v>
+        <v>0.005686819187221426</v>
       </c>
       <c r="AB63" s="186" t="n">
         <v>0.0002046798986735987</v>
@@ -7032,10 +7032,10 @@
         <v>1020.643796130887</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>39.13928972664274</v>
+        <v>39.13928972664275</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>0.003997120704944832</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005764545014327062</v>
+        <v>0.005764545014327061</v>
       </c>
       <c r="E68" s="149" t="n">
         <v>0.007564491641164402</v>
@@ -7315,19 +7315,19 @@
         <v>0.003961364774395752</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.005725966454513651</v>
+        <v>0.00572596645451365</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.007529626870405944</v>
+        <v>0.007529626870405943</v>
       </c>
       <c r="K68" s="149" t="n">
         <v>0.009149819535264886</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.0105362959456824</v>
+        <v>0.01053629594568239</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>441.6666564947561</v>
+        <v>441.6666564947562</v>
       </c>
       <c r="N68" s="152" t="n">
         <v>684.1272546328629</v>
@@ -7350,16 +7350,16 @@
         <v>0.004138322018859465</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.005968181929553585</v>
+        <v>0.005968181929553584</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.007831713033179737</v>
+        <v>0.007831713033179736</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.009497133579799586</v>
+        <v>0.009497133579799585</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.0109131530015144</v>
+        <v>0.01091315300151439</v>
       </c>
       <c r="Y68" s="148" t="n">
         <v>0.004107399190480783</v>
@@ -7368,16 +7368,16 @@
         <v>0.005934830490476735</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.007801582617869247</v>
+        <v>0.007801582617869246</v>
       </c>
       <c r="AB68" s="149" t="n">
         <v>0.009477032283687386</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.01090927054974404</v>
+        <v>0.01090927054974403</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>441.6666564947561</v>
+        <v>441.6666564947562</v>
       </c>
       <c r="AE68" s="152" t="n">
         <v>684.1272546328629</v>
@@ -7504,19 +7504,19 @@
         <v>0.003278579483336601</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004761332460872311</v>
+        <v>0.00476133246087231</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.00627100543235078</v>
+        <v>0.006271005432350778</v>
       </c>
       <c r="F70" s="162" t="n">
         <v>0.007612934488469349</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.008756654254511657</v>
+        <v>0.008756654254511654</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.003248859378921728</v>
+        <v>0.003248859378921729</v>
       </c>
       <c r="I70" s="162" t="n">
         <v>0.00472862314300876</v>
@@ -7528,10 +7528,10 @@
         <v>0.007592257515538809</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.008751497304816183</v>
+        <v>0.00875149730481618</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>441.6666564947561</v>
+        <v>441.6666564947562</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>684.1272546328629</v>
@@ -7554,34 +7554,34 @@
         <v>0.003380587043784103</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.004910110562554425</v>
+        <v>0.004910110562554423</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.006467401142050911</v>
+        <v>0.00646740114205091</v>
       </c>
       <c r="W70" s="162" t="n">
         <v>0.007851519462039427</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.009031250209509921</v>
+        <v>0.009031250209509919</v>
       </c>
       <c r="Y70" s="161" t="n">
         <v>0.003353948524254506</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.004880761772433044</v>
+        <v>0.004880761772433043</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.006440333801081499</v>
+        <v>0.006440333801081498</v>
       </c>
       <c r="AB70" s="162" t="n">
         <v>0.00783284968458595</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.009026413393850361</v>
+        <v>0.009026413393850357</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>441.6666564947561</v>
+        <v>441.6666564947562</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>684.1272546328629</v>
@@ -7603,22 +7603,22 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.008933636187012024</v>
+        <v>0.008933636187012022</v>
       </c>
       <c r="D71" s="156" t="n">
         <v>0.01300501029810884</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>0.01704301169374895</v>
+        <v>0.01704301169374894</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.02060031929126705</v>
+        <v>0.02060031929126704</v>
       </c>
       <c r="G71" s="157" t="n">
         <v>0.0235150581018346</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.008893417117733136</v>
+        <v>0.008893417117733135</v>
       </c>
       <c r="I71" s="156" t="n">
         <v>0.01296977298485401</v>
@@ -7627,19 +7627,19 @@
         <v>0.01702665691299119</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.02060031929126705</v>
+        <v>0.02060031929126704</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>0.0235150581018346</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>74.60266285532475</v>
+        <v>74.60266285532474</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>117.1464600613191</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>166.9583040677298</v>
+        <v>166.9583040677297</v>
       </c>
       <c r="P71" s="159" t="n">
         <v>223.4945477325937</v>
@@ -7659,7 +7659,7 @@
         <v>0.01583538940936581</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>0.02075221170091157</v>
+        <v>0.02075221170091156</v>
       </c>
       <c r="W71" s="156" t="n">
         <v>0.02508372315413866</v>
@@ -7674,7 +7674,7 @@
         <v>0.01578926442697879</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.02073080078123446</v>
+        <v>0.02073080078123445</v>
       </c>
       <c r="AB71" s="156" t="n">
         <v>0.02508372315413866</v>
@@ -7683,13 +7683,13 @@
         <v>0.02863281869761861</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>74.60266285532475</v>
+        <v>74.60266285532474</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>117.1464600613191</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>166.9583040677298</v>
+        <v>166.9583040677297</v>
       </c>
       <c r="AG71" s="159" t="n">
         <v>223.4945477325937</v>
@@ -7708,31 +7708,31 @@
         <v>0.003608670699454351</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005247654335413232</v>
+        <v>0.005247654335413231</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.006918815122292312</v>
+        <v>0.00691881512229231</v>
       </c>
       <c r="F72" s="162" t="n">
         <v>0.008412293986845948</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.009685090832465262</v>
+        <v>0.009685090832465259</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.003576915338331084</v>
+        <v>0.003576915338331083</v>
       </c>
       <c r="I72" s="162" t="n">
         <v>0.005212886955242683</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.006887187102516235</v>
+        <v>0.006887187102516233</v>
       </c>
       <c r="K72" s="162" t="n">
         <v>0.008390848616347675</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.009679745727440835</v>
+        <v>0.009679745727440832</v>
       </c>
       <c r="M72" s="164" t="n">
         <v>516.2693193500809</v>
@@ -7761,7 +7761,7 @@
         <v>0.005460943271554864</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.007201771036668175</v>
+        <v>0.007201771036668173</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>0.008758408050172023</v>
@@ -7776,7 +7776,7 @@
         <v>0.005429143306793931</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.007172794242298035</v>
+        <v>0.007172794242298033</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.008738675386721554</v>
@@ -7912,7 +7912,7 @@
         <v>0.00338593282778663</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.004909212177176243</v>
+        <v>0.004909212177176242</v>
       </c>
       <c r="E74" s="180" t="n">
         <v>0.006455575698620613</v>
@@ -7921,22 +7921,22 @@
         <v>0.007827929103269437</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.008995317143949483</v>
+        <v>0.00899531714394948</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.003357941674850544</v>
+        <v>0.003357941674850543</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>0.004878744273688548</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.006427997744635361</v>
+        <v>0.006427997744635359</v>
       </c>
       <c r="K74" s="180" t="n">
         <v>0.007809316397118755</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.008990663693271285</v>
+        <v>0.008990663693271282</v>
       </c>
       <c r="M74" s="182" t="n">
         <v>516.2693193500809</v>
@@ -7965,13 +7965,13 @@
         <v>0.004887099403816475</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.006417266164005201</v>
+        <v>0.006417266164005199</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.007769999639227207</v>
+        <v>0.007769999639227208</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.008920041387393903</v>
+        <v>0.0089200413873939</v>
       </c>
       <c r="Y74" s="185" t="n">
         <v>0.003352802870153375</v>
@@ -7980,13 +7980,13 @@
         <v>0.004861583482933754</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.006394207393993326</v>
+        <v>0.006394207393993324</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.007754418655259421</v>
+        <v>0.007754418655259422</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.008915993778290152</v>
+        <v>0.008915993778290148</v>
       </c>
       <c r="AD74" s="188" t="n">
         <v>516.2693193500809</v>
@@ -8260,19 +8260,19 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>492.3939924411048</v>
+        <v>492.3939924411047</v>
       </c>
       <c r="D79" s="149" t="n">
         <v>533.5255943458196</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>571.9241132683015</v>
+        <v>571.9241132683014</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>608.053968529037</v>
+        <v>608.0539685290368</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>638.8345717162155</v>
+        <v>638.8345717162154</v>
       </c>
       <c r="H79" s="148" t="n">
         <v>487.989320504446</v>
@@ -8281,25 +8281,25 @@
         <v>529.9550351772642</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>569.2881128539678</v>
+        <v>569.2881128539677</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>606.5116226352355</v>
+        <v>606.5116226352353</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>638.5621106475672</v>
+        <v>638.5621106475671</v>
       </c>
       <c r="M79" s="151" t="n">
         <v>54407666.01081879</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>63317989.40402257</v>
+        <v>63317989.40402258</v>
       </c>
       <c r="O79" s="152" t="n">
         <v>72588972.45591657</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>83476240.2494895</v>
+        <v>83476240.24948949</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>97096102.72248495</v>
@@ -8310,22 +8310,22 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>509.7881828668142</v>
+        <v>509.7881828668141</v>
       </c>
       <c r="U79" s="149" t="n">
         <v>552.3727897371219</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>592.1277654004582</v>
+        <v>592.1277654004581</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>629.5339351412766</v>
+        <v>629.5339351412764</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>661.4018864307372</v>
+        <v>661.4018864307371</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>505.9788871144708</v>
+        <v>505.9788871144707</v>
       </c>
       <c r="Z79" s="149" t="n">
         <v>549.2860159654643</v>
@@ -8334,22 +8334,22 @@
         <v>589.8497126407614</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>628.2014859410391</v>
+        <v>628.2014859410389</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>661.1665867951016</v>
+        <v>661.1665867951015</v>
       </c>
       <c r="AD79" s="151" t="n">
         <v>54407666.01081879</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>63317989.40402257</v>
+        <v>63317989.40402258</v>
       </c>
       <c r="AF79" s="152" t="n">
         <v>72588972.45591657</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>83476240.2494895</v>
+        <v>83476240.24948949</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>97096102.72248495</v>
@@ -8415,10 +8415,10 @@
         <v>1125.896803851121</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1207.84665892811</v>
+        <v>1207.846658928109</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1286.198970681339</v>
+        <v>1286.198970681338</v>
       </c>
       <c r="W80" s="156" t="n">
         <v>1352.780011904209</v>
@@ -8467,16 +8467,16 @@
         <v>603.8122770835906</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>648.3205462268121</v>
+        <v>648.320546226812</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>691.3845825709798</v>
+        <v>691.3845825709797</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>731.9164308156736</v>
+        <v>731.9164308156733</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>765.9928086509489</v>
+        <v>765.9928086509487</v>
       </c>
       <c r="H81" s="161" t="n">
         <v>598.3387590514326</v>
@@ -8488,10 +8488,10 @@
         <v>688.0648887299193</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>729.9285224407473</v>
+        <v>729.9285224407471</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>765.5417018393179</v>
+        <v>765.5417018393177</v>
       </c>
       <c r="M81" s="164" t="n">
         <v>81341248.83212879</v>
@@ -8503,7 +8503,7 @@
         <v>105850887.1801753</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>121072548.8015085</v>
+        <v>121072548.8015084</v>
       </c>
       <c r="Q81" s="166" t="n">
         <v>140143546.3114672</v>
@@ -8514,34 +8514,34 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>622.5988941738875</v>
+        <v>622.5988941738873</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>668.5787199506156</v>
+        <v>668.5787199506154</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>713.0374047913643</v>
+        <v>713.0374047913642</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>754.8542693805729</v>
+        <v>754.8542693805725</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>790.0132302297658</v>
+        <v>790.0132302297657</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>617.6929081463862</v>
+        <v>617.6929081463861</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>664.5824807047841</v>
+        <v>664.582480704784</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>710.0532035433632</v>
+        <v>710.053203543363</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>753.059335127747</v>
+        <v>753.0593351277466</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>789.5901273066276</v>
+        <v>789.5901273066274</v>
       </c>
       <c r="AD81" s="164" t="n">
         <v>81341248.83212879</v>
@@ -8553,7 +8553,7 @@
         <v>105850887.1801753</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>121072548.8015085</v>
+        <v>121072548.8015084</v>
       </c>
       <c r="AH81" s="166" t="n">
         <v>140143546.3114672</v>
@@ -8572,7 +8572,7 @@
         <v>1329.75965481879</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1400.935940050707</v>
+        <v>1400.935940050706</v>
       </c>
       <c r="F82" s="156" t="n">
         <v>1458.479385810898</v>
@@ -8581,7 +8581,7 @@
         <v>1495.424406980467</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>1241.493175674777</v>
+        <v>1241.493175674776</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>1326.15664671373</v>
@@ -8590,10 +8590,10 @@
         <v>1399.591576708892</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>1458.479385810897</v>
+        <v>1458.479385810898</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1495.424406980468</v>
+        <v>1495.424406980467</v>
       </c>
       <c r="M82" s="158" t="n">
         <v>10414298.08092253</v>
@@ -8602,10 +8602,10 @@
         <v>11978201.68716326</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>13723976.30544289</v>
+        <v>13723976.3054429</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>15823162.0636725</v>
+        <v>15823162.06367251</v>
       </c>
       <c r="Q82" s="160" t="n">
         <v>18367242.71753023</v>
@@ -8619,7 +8619,7 @@
         <v>1518.525132388068</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>1619.165342605034</v>
+        <v>1619.165342605035</v>
       </c>
       <c r="V82" s="156" t="n">
         <v>1705.832263085935</v>
@@ -8631,7 +8631,7 @@
         <v>1820.884972328644</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>1511.176905377552</v>
+        <v>1511.176905377551</v>
       </c>
       <c r="Z82" s="156" t="n">
         <v>1614.449072548224</v>
@@ -8652,10 +8652,10 @@
         <v>11978201.68716326</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>13723976.30544289</v>
+        <v>13723976.3054429</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>15823162.0636725</v>
+        <v>15823162.06367251</v>
       </c>
       <c r="AH82" s="160" t="n">
         <v>18367242.71753023</v>
@@ -8668,22 +8668,22 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>641.3620590012418</v>
+        <v>641.3620590012416</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>688.5208974801112</v>
+        <v>688.5208974801111</v>
       </c>
       <c r="E83" s="162" t="n">
         <v>734.0557650538308</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>776.6355954560321</v>
+        <v>776.635595456032</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>811.880628499918</v>
+        <v>811.8806284999177</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>635.7182401298146</v>
+        <v>635.7182401298145</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>683.9592273951525</v>
@@ -8692,10 +8692,10 @@
         <v>730.7001716691974</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>774.655726693392</v>
+        <v>774.6557266933919</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>811.4325596793259</v>
+        <v>811.4325596793255</v>
       </c>
       <c r="M83" s="164" t="n">
         <v>91755546.91305134</v>
@@ -8724,13 +8724,13 @@
         <v>716.5055703164653</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>764.0761394289833</v>
+        <v>764.0761394289831</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>808.5893647949633</v>
+        <v>808.5893647949631</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>845.4769554355006</v>
+        <v>845.4769554355005</v>
       </c>
       <c r="Y83" s="161" t="n">
         <v>662.1263568536295</v>
@@ -8739,13 +8739,13 @@
         <v>712.3332413333466</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>761.0018293651622</v>
+        <v>761.0018293651621</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>806.7676157152529</v>
+        <v>806.7676157152528</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>845.0484980471736</v>
+        <v>845.0484980471734</v>
       </c>
       <c r="AD83" s="164" t="n">
         <v>91755546.91305134</v>
@@ -8770,46 +8770,46 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>6868.847682808321</v>
+        <v>6868.847682808318</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>7154.647677011851</v>
+        <v>7154.647677011848</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>7527.196461235634</v>
+        <v>7527.196461235631</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>7772.2755948511</v>
+        <v>7772.275594851098</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>8072.362620025199</v>
+        <v>8072.362620025197</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>6868.1897528715</v>
+        <v>6868.189752871496</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>7154.019064805534</v>
+        <v>7154.019064805531</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>7526.582785221711</v>
+        <v>7526.582785221708</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>7771.701282204616</v>
+        <v>7771.701282204614</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>8071.827715194443</v>
+        <v>8071.82771519444</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>64644067.7560777</v>
+        <v>64644067.75607767</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>75314150.40606532</v>
+        <v>75314150.40606529</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>87986213.01955858</v>
+        <v>87986213.01955855</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>102272286.9730654</v>
+        <v>102272286.9730653</v>
       </c>
       <c r="Q84" s="160" t="n">
         <v>120853005.589122</v>
@@ -8820,46 +8820,46 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>4196.782010195626</v>
+        <v>4196.782010195624</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>4371.402314732208</v>
+        <v>4371.402314732206</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>4599.025070069153</v>
+        <v>4599.025070069151</v>
       </c>
       <c r="W84" s="156" t="n">
         <v>4748.765426316389</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>4932.114932216174</v>
+        <v>4932.114932216172</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>4196.490360162995</v>
+        <v>4196.490360162993</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>4371.123661396279</v>
+        <v>4371.123661396277</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>4598.753038171793</v>
+        <v>4598.753038171792</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>4748.510844048376</v>
+        <v>4748.510844048375</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>4931.877819206999</v>
+        <v>4931.877819206998</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>64644067.7560777</v>
+        <v>64644067.75607767</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>75314150.40606532</v>
+        <v>75314150.40606529</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>87986213.01955858</v>
+        <v>87986213.01955855</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>102272286.9730654</v>
+        <v>102272286.9730653</v>
       </c>
       <c r="AH84" s="160" t="n">
         <v>120853005.589122</v>
@@ -8881,7 +8881,7 @@
         <v>1188.88083631219</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>1262.59178768873</v>
+        <v>1262.591787688729</v>
       </c>
       <c r="G85" s="181" t="n">
         <v>1328.973294983668</v>
@@ -8914,7 +8914,7 @@
         <v>239167997.8382463</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>279363794.6181195</v>
+        <v>279363794.6181194</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8937,19 +8937,19 @@
         <v>1317.852011695802</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>1015.70451177239</v>
+        <v>1015.704511772389</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>1094.821293132168</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>1177.579040045757</v>
+        <v>1177.579040045756</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>1250.735051795708</v>
+        <v>1250.735051795707</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>1317.254015613915</v>
+        <v>1317.254015613914</v>
       </c>
       <c r="AD85" s="188" t="n">
         <v>156399614.669129</v>
@@ -8964,7 +8964,7 @@
         <v>239167997.8382463</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>279363794.6181195</v>
+        <v>279363794.6181194</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9284,7 +9284,7 @@
         <v>110496.2019156367</v>
       </c>
       <c r="D90" s="75" t="n">
-        <v>118678.4478102867</v>
+        <v>118678.4478102868</v>
       </c>
       <c r="E90" s="75" t="n">
         <v>126920.636447905</v>
@@ -9317,7 +9317,7 @@
         <v>119478.0409678406</v>
       </c>
       <c r="O90" s="75" t="n">
-        <v>127508.3227928507</v>
+        <v>127508.3227928508</v>
       </c>
       <c r="P90" s="75" t="n">
         <v>137633.3727732919</v>
@@ -9370,7 +9370,7 @@
         <v>123063.5039744874</v>
       </c>
       <c r="AG90" s="75" t="n">
-        <v>132881.316134493</v>
+        <v>132881.3161344931</v>
       </c>
       <c r="AH90" s="76" t="n">
         <v>146855.7314626903</v>
@@ -9410,7 +9410,7 @@
         <v>25005.54406696305</v>
       </c>
       <c r="E91" s="80" t="n">
-        <v>26179.22989067978</v>
+        <v>26179.22989067979</v>
       </c>
       <c r="F91" s="80" t="n">
         <v>28134.28005717414</v>
@@ -9563,7 +9563,7 @@
         <v>153838.5244094676</v>
       </c>
       <c r="P92" s="86" t="n">
-        <v>165869.0475564155</v>
+        <v>165869.0475564156</v>
       </c>
       <c r="Q92" s="87" t="n">
         <v>183064.5489001492</v>
@@ -9583,7 +9583,7 @@
         <v>148450.6794018013</v>
       </c>
       <c r="W92" s="86" t="n">
-        <v>160391.950754759</v>
+        <v>160391.9507547591</v>
       </c>
       <c r="X92" s="87" t="n">
         <v>177393.9232267138</v>
@@ -9607,7 +9607,7 @@
         <v>131685.5799368379</v>
       </c>
       <c r="AE92" s="86" t="n">
-        <v>140168.1308227071</v>
+        <v>140168.1308227072</v>
       </c>
       <c r="AF92" s="86" t="n">
         <v>149074.5857520956</v>
@@ -9639,10 +9639,10 @@
         <v>8350.761245883758</v>
       </c>
       <c r="D93" s="80" t="n">
-        <v>9007.794486587551</v>
+        <v>9007.794486587552</v>
       </c>
       <c r="E93" s="80" t="n">
-        <v>9796.291117312727</v>
+        <v>9796.291117312729</v>
       </c>
       <c r="F93" s="80" t="n">
         <v>10849.08173376411</v>
@@ -9669,10 +9669,10 @@
         <v>8388.526239994959</v>
       </c>
       <c r="N93" s="80" t="n">
-        <v>9032.267580791255</v>
+        <v>9032.267580791256</v>
       </c>
       <c r="O93" s="80" t="n">
-        <v>9805.700844323821</v>
+        <v>9805.700844323823</v>
       </c>
       <c r="P93" s="80" t="n">
         <v>10849.08173376411</v>
@@ -9689,13 +9689,13 @@
         <v>6858.166426619998</v>
       </c>
       <c r="U93" s="80" t="n">
-        <v>7397.763138810662</v>
+        <v>7397.763138810664</v>
       </c>
       <c r="V93" s="80" t="n">
-        <v>8045.325793413907</v>
+        <v>8045.325793413908</v>
       </c>
       <c r="W93" s="80" t="n">
-        <v>8909.943167496587</v>
+        <v>8909.943167496589</v>
       </c>
       <c r="X93" s="81" t="n">
         <v>10086.98682050258</v>
@@ -9719,13 +9719,13 @@
         <v>6891.514847707808</v>
       </c>
       <c r="AE93" s="80" t="n">
-        <v>7419.374132537382</v>
+        <v>7419.374132537384</v>
       </c>
       <c r="AF93" s="80" t="n">
-        <v>8053.63506357461</v>
+        <v>8053.635063574611</v>
       </c>
       <c r="AG93" s="80" t="n">
-        <v>8909.943167496587</v>
+        <v>8909.943167496589</v>
       </c>
       <c r="AH93" s="81" t="n">
         <v>10086.98682050258</v>
@@ -9759,16 +9759,16 @@
         <v>143063.5716991698</v>
       </c>
       <c r="D94" s="86" t="n">
-        <v>152691.7863638373</v>
+        <v>152691.7863638374</v>
       </c>
       <c r="E94" s="86" t="n">
         <v>162896.1574558975</v>
       </c>
       <c r="F94" s="86" t="n">
-        <v>176267.6236656359</v>
+        <v>176267.623665636</v>
       </c>
       <c r="G94" s="87" t="n">
-        <v>195239.0332577241</v>
+        <v>195239.0332577242</v>
       </c>
       <c r="H94" s="85" t="n">
         <v>1270.098661326248</v>
@@ -9812,10 +9812,10 @@
         <v>146728.0788042392</v>
       </c>
       <c r="V94" s="86" t="n">
-        <v>156496.0051952152</v>
+        <v>156496.0051952153</v>
       </c>
       <c r="W94" s="86" t="n">
-        <v>169301.8939222556</v>
+        <v>169301.8939222557</v>
       </c>
       <c r="X94" s="87" t="n">
         <v>187480.9100472164</v>
@@ -9824,7 +9824,7 @@
         <v>1071.011065912703</v>
       </c>
       <c r="Z94" s="86" t="n">
-        <v>859.4261510053072</v>
+        <v>859.4261510053074</v>
       </c>
       <c r="AA94" s="86" t="n">
         <v>632.2156204549408</v>
@@ -9991,7 +9991,7 @@
         <v>152474.7671050415</v>
       </c>
       <c r="D96" s="133" t="n">
-        <v>163218.3914191851</v>
+        <v>163218.3914191852</v>
       </c>
       <c r="E96" s="133" t="n">
         <v>174585.2655418469</v>
@@ -10030,7 +10030,7 @@
         <v>189877.7044281543</v>
       </c>
       <c r="Q96" s="134" t="n">
-        <v>210319.0415807613</v>
+        <v>210319.0415807614</v>
       </c>
       <c r="S96" s="51" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>163956.9095051442</v>
       </c>
       <c r="V96" s="136" t="n">
-        <v>175627.4975613213</v>
+        <v>175627.4975613214</v>
       </c>
       <c r="W96" s="136" t="n">
         <v>190838.4992905267</v>
@@ -10056,7 +10056,7 @@
         <v>1072.081569346541</v>
       </c>
       <c r="Z96" s="136" t="n">
-        <v>860.5244661116376</v>
+        <v>860.5244661116377</v>
       </c>
       <c r="AA96" s="136" t="n">
         <v>633.3473133561454</v>
@@ -10080,7 +10080,7 @@
         <v>191221.9518393345</v>
       </c>
       <c r="AH96" s="137" t="n">
-        <v>212080.4273941956</v>
+        <v>212080.4273941957</v>
       </c>
       <c r="AJ96" s="138" t="n"/>
       <c r="AK96" s="139" t="n"/>
